--- a/pratimai 2/Adresai.xlsx
+++ b/pratimai 2/Adresai.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rober\Desktop\Mokslai\komp tinklai\pratimai 2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Home\Desktop\mokslai\semestras 4\komp-tinklai\pratimai 2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F041826-4020-4E91-B8A4-0016B764FA8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A472D1C-4556-41E1-8B16-4887FD182342}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20520" yWindow="6585" windowWidth="20640" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="45">
   <si>
     <t>Potinklis</t>
   </si>
@@ -154,9 +154,6 @@
   </si>
   <si>
     <t>PC31</t>
-  </si>
-  <si>
-    <t>(40 adr.)</t>
   </si>
   <si>
     <t>26.3.29.60</t>
@@ -524,16 +521,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E15"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="35.44140625" customWidth="1"/>
+    <col min="1" max="1" width="35.42578125" customWidth="1"/>
     <col min="2" max="2" width="31" customWidth="1"/>
-    <col min="3" max="3" width="34.5546875" customWidth="1"/>
-    <col min="4" max="4" width="27.33203125" customWidth="1"/>
-    <col min="5" max="5" width="27.109375" customWidth="1"/>
+    <col min="3" max="3" width="34.5703125" customWidth="1"/>
+    <col min="4" max="4" width="27.28515625" customWidth="1"/>
+    <col min="5" max="5" width="27.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="42" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -550,7 +547,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>23</v>
       </c>
@@ -567,7 +564,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="42" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>26</v>
       </c>
@@ -584,7 +581,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>5</v>
       </c>
@@ -601,7 +598,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4"/>
       <c r="B5" s="4" t="s">
         <v>31</v>
@@ -616,7 +613,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>33</v>
       </c>
@@ -633,7 +630,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>34</v>
       </c>
@@ -650,7 +647,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="42" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
         <v>36</v>
       </c>
@@ -667,7 +664,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>11</v>
       </c>
@@ -684,7 +681,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="4"/>
       <c r="B10" s="4" t="s">
         <v>39</v>
@@ -699,7 +696,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>33</v>
       </c>
@@ -716,7 +713,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>40</v>
       </c>
@@ -733,9 +730,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="42" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="4" t="s">
-        <v>42</v>
+    <row r="13" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="4">
+        <v>2</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>15</v>
@@ -744,18 +741,18 @@
         <v>27</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
         <v>17</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>30</v>
@@ -767,10 +764,10 @@
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="4"/>
       <c r="B15" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>32</v>

--- a/pratimai 2/Adresai.xlsx
+++ b/pratimai 2/Adresai.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Home\Desktop\mokslai\semestras 4\komp-tinklai\pratimai 2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rober\Desktop\Mokslai\komp tinklai\pratimai 2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A472D1C-4556-41E1-8B16-4887FD182342}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69E99B79-D4DB-493C-B16D-D626FF1E46DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20520" yWindow="6585" windowWidth="20640" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="13776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -521,16 +521,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="35.42578125" customWidth="1"/>
+    <col min="1" max="1" width="35.44140625" customWidth="1"/>
     <col min="2" max="2" width="31" customWidth="1"/>
-    <col min="3" max="3" width="34.5703125" customWidth="1"/>
-    <col min="4" max="4" width="27.28515625" customWidth="1"/>
-    <col min="5" max="5" width="27.140625" customWidth="1"/>
+    <col min="3" max="3" width="34.5546875" customWidth="1"/>
+    <col min="4" max="4" width="27.33203125" customWidth="1"/>
+    <col min="5" max="5" width="27.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -547,7 +547,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>23</v>
       </c>
@@ -564,7 +564,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
         <v>26</v>
       </c>
@@ -581,7 +581,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="4" t="s">
         <v>5</v>
       </c>
@@ -598,7 +598,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="4"/>
       <c r="B5" s="4" t="s">
         <v>31</v>
@@ -613,7 +613,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="s">
         <v>33</v>
       </c>
@@ -630,7 +630,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>34</v>
       </c>
@@ -647,7 +647,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="4" t="s">
         <v>36</v>
       </c>
@@ -664,7 +664,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="4" t="s">
         <v>11</v>
       </c>
@@ -681,7 +681,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="4"/>
       <c r="B10" s="4" t="s">
         <v>39</v>
@@ -696,7 +696,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="4" t="s">
         <v>33</v>
       </c>
@@ -713,7 +713,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>40</v>
       </c>
@@ -730,7 +730,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="4">
         <v>2</v>
       </c>
@@ -747,7 +747,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="4" t="s">
         <v>17</v>
       </c>
@@ -764,7 +764,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="4"/>
       <c r="B15" s="4" t="s">
         <v>44</v>
